--- a/excel/product_review_analysis.xlsx
+++ b/excel/product_review_analysis.xlsx
@@ -1,30 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="16729"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Data-Science\DS Sprint Assessment\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Rating Analysis" sheetId="2" r:id="rId2"/>
     <sheet name="Sentiment Analysis" sheetId="3" r:id="rId3"/>
-    <sheet name="Top Products" sheetId="4" r:id="rId4"/>
-    <sheet name="Lowest Rated" sheetId="5" r:id="rId5"/>
-    <sheet name="Price Analysis" sheetId="6" r:id="rId6"/>
-    <sheet name="Review Length" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId4"/>
+    <sheet name="Top Products" sheetId="4" r:id="rId5"/>
+    <sheet name="Lowest Rated" sheetId="5" r:id="rId6"/>
+    <sheet name="Price Analysis" sheetId="6" r:id="rId7"/>
+    <sheet name="Review Length" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lowest Rated'!$A$1:$D$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Price Analysis'!$A$1:$C$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Lowest Rated'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Price Analysis'!$A$1:$C$523</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rating Analysis'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Review Length'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Review Length'!$A$1:$C$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sentiment Analysis'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Summary!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Top Products'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Top Products'!$A$1:$D$21</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -232,8 +238,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,12 +308,30 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -325,13 +349,15 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -343,6 +369,7 @@
               <a:srgbClr val="4472C4"/>
             </a:solidFill>
           </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
               <c:f>'Rating Analysis'!$A$2:$A$6</c:f>
@@ -391,7 +418,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A163-426A-A056-18E9A674EADB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:barChart>
@@ -400,6 +441,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -417,21 +459,25 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -450,9 +496,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -461,9 +509,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -474,8 +524,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -493,13 +553,15 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -511,6 +573,7 @@
               <a:srgbClr val="70AD47"/>
             </a:solidFill>
           </c:spPr>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>'Sentiment Analysis'!$A$2:$A$4</c:f>
@@ -541,12 +604,26 @@
                   <c:v>3.28</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.6</c:v>
+                  <c:v>4.5999999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC51-47EA-B032-F87525EC7784}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:barChart>
@@ -555,13 +632,18 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50020002"/>
@@ -570,6 +652,7 @@
           <c:max val="5"/>
           <c:min val="0"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -588,9 +671,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -599,9 +684,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -724,7 +811,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -756,9 +843,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -790,6 +895,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -965,15 +1088,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="4" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="28" customHeight="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +1104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -989,7 +1112,7 @@
         <v>170674</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -997,15 +1120,15 @@
         <v>958</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1013,7 +1136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1021,7 +1144,7 @@
         <v>4488.55</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1029,7 +1152,7 @@
         <v>16202</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1044,15 +1167,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="4" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="28" customHeight="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1060,7 +1183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1068,7 +1191,7 @@
         <v>19880</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1076,7 +1199,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1084,7 +1207,7 @@
         <v>14389</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1092,7 +1215,7 @@
         <v>33551</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1108,15 +1231,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="4" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="28" customHeight="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,7 +1253,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1144,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1158,7 +1281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1166,7 +1289,7 @@
         <v>134699</v>
       </c>
       <c r="C4">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -1180,324 +1303,24 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2">
-        <v>4362</v>
-      </c>
-      <c r="C2">
-        <v>4.27</v>
-      </c>
-      <c r="D2">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3">
-        <v>2805</v>
-      </c>
-      <c r="C3">
-        <v>4.48</v>
-      </c>
-      <c r="D3">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
-        <v>2122</v>
-      </c>
-      <c r="C4">
-        <v>4.13</v>
-      </c>
-      <c r="D4">
-        <v>13999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
-        <v>1743</v>
-      </c>
-      <c r="C5">
-        <v>4.32</v>
-      </c>
-      <c r="D5">
-        <v>8499</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>1646</v>
-      </c>
-      <c r="C6">
-        <v>4.45</v>
-      </c>
-      <c r="D6">
-        <v>30999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7">
-        <v>1642</v>
-      </c>
-      <c r="C7">
-        <v>4.34</v>
-      </c>
-      <c r="D7">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>1613</v>
-      </c>
-      <c r="C8">
-        <v>4.04</v>
-      </c>
-      <c r="D8">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>1569</v>
-      </c>
-      <c r="C9">
-        <v>3.87</v>
-      </c>
-      <c r="D9">
-        <v>7499</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10">
-        <v>1545</v>
-      </c>
-      <c r="C10">
-        <v>4.7</v>
-      </c>
-      <c r="D10">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11">
-        <v>1509</v>
-      </c>
-      <c r="C11">
-        <v>3.97</v>
-      </c>
-      <c r="D11">
-        <v>3499</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12">
-        <v>1506</v>
-      </c>
-      <c r="C12">
-        <v>4.12</v>
-      </c>
-      <c r="D12">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13">
-        <v>1480</v>
-      </c>
-      <c r="C13">
-        <v>4.27</v>
-      </c>
-      <c r="D13">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14">
-        <v>1475</v>
-      </c>
-      <c r="C14">
-        <v>3.94</v>
-      </c>
-      <c r="D14">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15">
-        <v>1440</v>
-      </c>
-      <c r="C15">
-        <v>4.42</v>
-      </c>
-      <c r="D15">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16">
-        <v>1438</v>
-      </c>
-      <c r="C16">
-        <v>3.7</v>
-      </c>
-      <c r="D16">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17">
-        <v>1436</v>
-      </c>
-      <c r="C17">
-        <v>4.49</v>
-      </c>
-      <c r="D17">
-        <v>24490</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18">
-        <v>1414</v>
-      </c>
-      <c r="C18">
-        <v>4.07</v>
-      </c>
-      <c r="D18">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19">
-        <v>1399</v>
-      </c>
-      <c r="C19">
-        <v>4.29</v>
-      </c>
-      <c r="D19">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20">
-        <v>1395</v>
-      </c>
-      <c r="C20">
-        <v>4.38</v>
-      </c>
-      <c r="D20">
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21">
-        <v>1378</v>
-      </c>
-      <c r="C21">
-        <v>4.16</v>
-      </c>
-      <c r="D21">
-        <v>5499</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="4" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="28" customHeight="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1511,284 +1334,284 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>4362</v>
       </c>
       <c r="C2">
-        <v>2.25</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="D2">
-        <v>3999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>2805</v>
       </c>
       <c r="C3">
-        <v>2.29</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="D3">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>51</v>
+        <v>2122</v>
       </c>
       <c r="C4">
-        <v>2.49</v>
+        <v>4.13</v>
       </c>
       <c r="D4">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>13999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B5">
-        <v>188</v>
+        <v>1743</v>
       </c>
       <c r="C5">
-        <v>2.62</v>
+        <v>4.32</v>
       </c>
       <c r="D5">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B6">
-        <v>92</v>
+        <v>1646</v>
       </c>
       <c r="C6">
-        <v>2.62</v>
+        <v>4.45</v>
       </c>
       <c r="D6">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>30999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B7">
+        <v>1642</v>
+      </c>
+      <c r="C7">
+        <v>4.34</v>
+      </c>
+      <c r="D7">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>1613</v>
+      </c>
+      <c r="C8">
+        <v>4.04</v>
+      </c>
+      <c r="D8">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9">
+        <v>1569</v>
+      </c>
+      <c r="C9">
+        <v>3.87</v>
+      </c>
+      <c r="D9">
+        <v>7499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10">
+        <v>1545</v>
+      </c>
+      <c r="C10">
+        <v>4.7</v>
+      </c>
+      <c r="D10">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11">
+        <v>1509</v>
+      </c>
+      <c r="C11">
+        <v>3.97</v>
+      </c>
+      <c r="D11">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12">
+        <v>1506</v>
+      </c>
+      <c r="C12">
+        <v>4.12</v>
+      </c>
+      <c r="D12">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13">
+        <v>1480</v>
+      </c>
+      <c r="C13">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="D13">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14">
+        <v>1475</v>
+      </c>
+      <c r="C14">
+        <v>3.94</v>
+      </c>
+      <c r="D14">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <v>1440</v>
+      </c>
+      <c r="C15">
+        <v>4.42</v>
+      </c>
+      <c r="D15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16">
+        <v>1438</v>
+      </c>
+      <c r="C16">
+        <v>3.7</v>
+      </c>
+      <c r="D16">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>35</v>
       </c>
-      <c r="C7">
-        <v>2.63</v>
-      </c>
-      <c r="D7">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8">
-        <v>99</v>
-      </c>
-      <c r="C8">
-        <v>2.67</v>
-      </c>
-      <c r="D8">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9">
-        <v>185</v>
-      </c>
-      <c r="C9">
-        <v>2.68</v>
-      </c>
-      <c r="D9">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10">
-        <v>198</v>
-      </c>
-      <c r="C10">
-        <v>2.69</v>
-      </c>
-      <c r="D10">
-        <v>4687</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11">
-        <v>96</v>
-      </c>
-      <c r="C11">
-        <v>2.71</v>
-      </c>
-      <c r="D11">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12">
-        <v>80</v>
-      </c>
-      <c r="C12">
-        <v>2.76</v>
-      </c>
-      <c r="D12">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13">
-        <v>100</v>
-      </c>
-      <c r="C13">
-        <v>2.77</v>
-      </c>
-      <c r="D13">
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14">
-        <v>566</v>
-      </c>
-      <c r="C14">
-        <v>2.8</v>
-      </c>
-      <c r="D14">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15">
+      <c r="B17">
+        <v>1436</v>
+      </c>
+      <c r="C17">
+        <v>4.49</v>
+      </c>
+      <c r="D17">
+        <v>24490</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18">
+        <v>1414</v>
+      </c>
+      <c r="C18">
+        <v>4.07</v>
+      </c>
+      <c r="D18">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>37</v>
       </c>
-      <c r="C15">
-        <v>2.86</v>
-      </c>
-      <c r="D15">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16">
-        <v>95</v>
-      </c>
-      <c r="C16">
-        <v>2.88</v>
-      </c>
-      <c r="D16">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17">
-        <v>89</v>
-      </c>
-      <c r="C17">
-        <v>2.93</v>
-      </c>
-      <c r="D17">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18">
-        <v>210</v>
-      </c>
-      <c r="C18">
-        <v>2.95</v>
-      </c>
-      <c r="D18">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
       <c r="B19">
-        <v>276</v>
+        <v>1399</v>
       </c>
       <c r="C19">
-        <v>2.96</v>
+        <v>4.29</v>
       </c>
       <c r="D19">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B20">
-        <v>86</v>
+        <v>1395</v>
       </c>
       <c r="C20">
-        <v>2.97</v>
+        <v>4.38</v>
       </c>
       <c r="D20">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B21">
-        <v>30</v>
+        <v>1378</v>
       </c>
       <c r="C21">
-        <v>2.97</v>
+        <v>4.16</v>
       </c>
       <c r="D21">
-        <v>259</v>
+        <v>5499</v>
       </c>
     </row>
   </sheetData>
@@ -1798,15 +1621,324 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C523"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="4" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="28" customHeight="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>2.25</v>
+      </c>
+      <c r="D2">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>2.29</v>
+      </c>
+      <c r="D3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4">
+        <v>51</v>
+      </c>
+      <c r="C4">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="D4">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5">
+        <v>188</v>
+      </c>
+      <c r="C5">
+        <v>2.62</v>
+      </c>
+      <c r="D5">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6">
+        <v>92</v>
+      </c>
+      <c r="C6">
+        <v>2.62</v>
+      </c>
+      <c r="D6">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7">
+        <v>35</v>
+      </c>
+      <c r="C7">
+        <v>2.63</v>
+      </c>
+      <c r="D7">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8">
+        <v>99</v>
+      </c>
+      <c r="C8">
+        <v>2.67</v>
+      </c>
+      <c r="D8">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9">
+        <v>185</v>
+      </c>
+      <c r="C9">
+        <v>2.68</v>
+      </c>
+      <c r="D9">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10">
+        <v>198</v>
+      </c>
+      <c r="C10">
+        <v>2.69</v>
+      </c>
+      <c r="D10">
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11">
+        <v>96</v>
+      </c>
+      <c r="C11">
+        <v>2.71</v>
+      </c>
+      <c r="D11">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12">
+        <v>80</v>
+      </c>
+      <c r="C12">
+        <v>2.76</v>
+      </c>
+      <c r="D12">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>2.77</v>
+      </c>
+      <c r="D13">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14">
+        <v>566</v>
+      </c>
+      <c r="C14">
+        <v>2.8</v>
+      </c>
+      <c r="D14">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15">
+        <v>37</v>
+      </c>
+      <c r="C15">
+        <v>2.86</v>
+      </c>
+      <c r="D15">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16">
+        <v>95</v>
+      </c>
+      <c r="C16">
+        <v>2.88</v>
+      </c>
+      <c r="D16">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17">
+        <v>89</v>
+      </c>
+      <c r="C17">
+        <v>2.93</v>
+      </c>
+      <c r="D17">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18">
+        <v>210</v>
+      </c>
+      <c r="C18">
+        <v>2.95</v>
+      </c>
+      <c r="D18">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19">
+        <v>276</v>
+      </c>
+      <c r="C19">
+        <v>2.96</v>
+      </c>
+      <c r="D19">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <v>2.97</v>
+      </c>
+      <c r="D20">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>2.97</v>
+      </c>
+      <c r="D21">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D21"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C523"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="4" width="22.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1817,7 +1949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>59</v>
       </c>
@@ -1828,7 +1960,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>79</v>
       </c>
@@ -1839,7 +1971,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>109</v>
       </c>
@@ -1850,7 +1982,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>113</v>
       </c>
@@ -1858,10 +1990,10 @@
         <v>1348</v>
       </c>
       <c r="C5">
-        <v>4.64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>4.6399999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>125</v>
       </c>
@@ -1872,7 +2004,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>127</v>
       </c>
@@ -1883,7 +2015,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>130</v>
       </c>
@@ -1894,7 +2026,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>134</v>
       </c>
@@ -1905,7 +2037,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>136</v>
       </c>
@@ -1913,10 +2045,10 @@
         <v>93</v>
       </c>
       <c r="C10">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>145</v>
       </c>
@@ -1924,10 +2056,10 @@
         <v>60</v>
       </c>
       <c r="C11">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>150</v>
       </c>
@@ -1938,7 +2070,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>152</v>
       </c>
@@ -1949,7 +2081,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>154</v>
       </c>
@@ -1960,7 +2092,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>155</v>
       </c>
@@ -1971,7 +2103,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>159</v>
       </c>
@@ -1982,7 +2114,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>160</v>
       </c>
@@ -1993,7 +2125,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>163</v>
       </c>
@@ -2004,7 +2136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>165</v>
       </c>
@@ -2015,7 +2147,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>166</v>
       </c>
@@ -2026,7 +2158,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>168</v>
       </c>
@@ -2037,7 +2169,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>169</v>
       </c>
@@ -2048,7 +2180,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>170</v>
       </c>
@@ -2059,7 +2191,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>171</v>
       </c>
@@ -2067,10 +2199,10 @@
         <v>780</v>
       </c>
       <c r="C24">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>173</v>
       </c>
@@ -2081,7 +2213,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>176</v>
       </c>
@@ -2092,7 +2224,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>178</v>
       </c>
@@ -2103,7 +2235,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>179</v>
       </c>
@@ -2114,7 +2246,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>180</v>
       </c>
@@ -2125,7 +2257,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>184</v>
       </c>
@@ -2136,7 +2268,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>185</v>
       </c>
@@ -2147,7 +2279,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>188</v>
       </c>
@@ -2158,7 +2290,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>189</v>
       </c>
@@ -2169,7 +2301,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>190</v>
       </c>
@@ -2180,7 +2312,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>193</v>
       </c>
@@ -2191,7 +2323,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>194</v>
       </c>
@@ -2202,7 +2334,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>195</v>
       </c>
@@ -2213,7 +2345,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>197</v>
       </c>
@@ -2224,7 +2356,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>198</v>
       </c>
@@ -2235,7 +2367,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>199</v>
       </c>
@@ -2246,7 +2378,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>200</v>
       </c>
@@ -2257,7 +2389,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>202</v>
       </c>
@@ -2268,7 +2400,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>203</v>
       </c>
@@ -2279,7 +2411,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>204</v>
       </c>
@@ -2290,7 +2422,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>205</v>
       </c>
@@ -2301,7 +2433,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>206</v>
       </c>
@@ -2312,7 +2444,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>209</v>
       </c>
@@ -2323,7 +2455,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>210</v>
       </c>
@@ -2334,7 +2466,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>211</v>
       </c>
@@ -2345,7 +2477,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>212</v>
       </c>
@@ -2356,7 +2488,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>214</v>
       </c>
@@ -2364,10 +2496,10 @@
         <v>70</v>
       </c>
       <c r="C51">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>215</v>
       </c>
@@ -2378,7 +2510,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>216</v>
       </c>
@@ -2389,7 +2521,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>218</v>
       </c>
@@ -2397,10 +2529,10 @@
         <v>4169</v>
       </c>
       <c r="C54">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>219</v>
       </c>
@@ -2411,7 +2543,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>220</v>
       </c>
@@ -2419,10 +2551,10 @@
         <v>99</v>
       </c>
       <c r="C56">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>4.6100000000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>221</v>
       </c>
@@ -2430,10 +2562,10 @@
         <v>16</v>
       </c>
       <c r="C57">
-        <v>4.69</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>224</v>
       </c>
@@ -2444,7 +2576,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>225</v>
       </c>
@@ -2455,7 +2587,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>227</v>
       </c>
@@ -2466,7 +2598,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>229</v>
       </c>
@@ -2477,7 +2609,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>230</v>
       </c>
@@ -2488,7 +2620,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>231</v>
       </c>
@@ -2499,7 +2631,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>232</v>
       </c>
@@ -2507,10 +2639,10 @@
         <v>99</v>
       </c>
       <c r="C64">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>4.2300000000000004</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>233</v>
       </c>
@@ -2521,7 +2653,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>235</v>
       </c>
@@ -2532,7 +2664,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>236</v>
       </c>
@@ -2543,7 +2675,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>237</v>
       </c>
@@ -2554,7 +2686,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>239</v>
       </c>
@@ -2565,7 +2697,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>240</v>
       </c>
@@ -2576,7 +2708,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>241</v>
       </c>
@@ -2587,7 +2719,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>242</v>
       </c>
@@ -2595,10 +2727,10 @@
         <v>47</v>
       </c>
       <c r="C72">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>244</v>
       </c>
@@ -2609,7 +2741,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>245</v>
       </c>
@@ -2620,7 +2752,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>247</v>
       </c>
@@ -2631,7 +2763,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>249</v>
       </c>
@@ -2642,7 +2774,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>253</v>
       </c>
@@ -2653,7 +2785,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>254</v>
       </c>
@@ -2661,10 +2793,10 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>255</v>
       </c>
@@ -2675,7 +2807,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>256</v>
       </c>
@@ -2686,7 +2818,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>257</v>
       </c>
@@ -2697,7 +2829,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>258</v>
       </c>
@@ -2708,7 +2840,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>259</v>
       </c>
@@ -2719,7 +2851,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>260</v>
       </c>
@@ -2730,7 +2862,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>261</v>
       </c>
@@ -2741,7 +2873,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>262</v>
       </c>
@@ -2749,10 +2881,10 @@
         <v>15</v>
       </c>
       <c r="C86">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>267</v>
       </c>
@@ -2760,10 +2892,10 @@
         <v>281</v>
       </c>
       <c r="C87">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>268</v>
       </c>
@@ -2774,7 +2906,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>269</v>
       </c>
@@ -2785,7 +2917,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>270</v>
       </c>
@@ -2796,7 +2928,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>275</v>
       </c>
@@ -2807,7 +2939,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>277</v>
       </c>
@@ -2818,7 +2950,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>278</v>
       </c>
@@ -2826,10 +2958,10 @@
         <v>188</v>
       </c>
       <c r="C93">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>279</v>
       </c>
@@ -2840,7 +2972,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>280</v>
       </c>
@@ -2851,7 +2983,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>281</v>
       </c>
@@ -2859,10 +2991,10 @@
         <v>31</v>
       </c>
       <c r="C96">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>283</v>
       </c>
@@ -2870,10 +3002,10 @@
         <v>157</v>
       </c>
       <c r="C97">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>284</v>
       </c>
@@ -2881,10 +3013,10 @@
         <v>202</v>
       </c>
       <c r="C98">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>285</v>
       </c>
@@ -2892,10 +3024,10 @@
         <v>205</v>
       </c>
       <c r="C99">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>287</v>
       </c>
@@ -2906,7 +3038,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>289</v>
       </c>
@@ -2917,7 +3049,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>290</v>
       </c>
@@ -2925,10 +3057,10 @@
         <v>483</v>
       </c>
       <c r="C102">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>293</v>
       </c>
@@ -2939,7 +3071,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>295</v>
       </c>
@@ -2950,7 +3082,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>296</v>
       </c>
@@ -2961,7 +3093,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>298</v>
       </c>
@@ -2972,7 +3104,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>299</v>
       </c>
@@ -2983,7 +3115,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>302</v>
       </c>
@@ -2994,7 +3126,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>303</v>
       </c>
@@ -3005,7 +3137,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>305</v>
       </c>
@@ -3016,7 +3148,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>306</v>
       </c>
@@ -3027,7 +3159,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>310</v>
       </c>
@@ -3038,7 +3170,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>315</v>
       </c>
@@ -3049,7 +3181,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>319</v>
       </c>
@@ -3057,10 +3189,10 @@
         <v>1068</v>
       </c>
       <c r="C114">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>321</v>
       </c>
@@ -3071,7 +3203,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>323</v>
       </c>
@@ -3082,7 +3214,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>324</v>
       </c>
@@ -3093,7 +3225,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>325</v>
       </c>
@@ -3101,10 +3233,10 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>329</v>
       </c>
@@ -3115,7 +3247,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>330</v>
       </c>
@@ -3126,7 +3258,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>335</v>
       </c>
@@ -3134,10 +3266,10 @@
         <v>48</v>
       </c>
       <c r="C121">
-        <v>4.69</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>338</v>
       </c>
@@ -3148,7 +3280,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>339</v>
       </c>
@@ -3159,7 +3291,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>340</v>
       </c>
@@ -3170,7 +3302,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>343</v>
       </c>
@@ -3178,10 +3310,10 @@
         <v>26</v>
       </c>
       <c r="C125">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>346</v>
       </c>
@@ -3189,10 +3321,10 @@
         <v>99</v>
       </c>
       <c r="C126">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
+        <v>4.1900000000000004</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>348</v>
       </c>
@@ -3203,7 +3335,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>349</v>
       </c>
@@ -3211,10 +3343,10 @@
         <v>1347</v>
       </c>
       <c r="C128">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>350</v>
       </c>
@@ -3225,7 +3357,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>354</v>
       </c>
@@ -3236,7 +3368,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>357</v>
       </c>
@@ -3247,7 +3379,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>359</v>
       </c>
@@ -3258,7 +3390,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>360</v>
       </c>
@@ -3269,7 +3401,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>361</v>
       </c>
@@ -3280,7 +3412,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>365</v>
       </c>
@@ -3291,7 +3423,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>366</v>
       </c>
@@ -3302,7 +3434,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>367</v>
       </c>
@@ -3313,7 +3445,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>368</v>
       </c>
@@ -3324,7 +3456,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>369</v>
       </c>
@@ -3335,7 +3467,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>373</v>
       </c>
@@ -3346,7 +3478,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>379</v>
       </c>
@@ -3357,7 +3489,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>385</v>
       </c>
@@ -3368,7 +3500,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>386</v>
       </c>
@@ -3379,7 +3511,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>387</v>
       </c>
@@ -3390,7 +3522,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>388</v>
       </c>
@@ -3398,10 +3530,10 @@
         <v>18</v>
       </c>
       <c r="C145">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>389</v>
       </c>
@@ -3412,7 +3544,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>390</v>
       </c>
@@ -3423,7 +3555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>394</v>
       </c>
@@ -3434,7 +3566,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>395</v>
       </c>
@@ -3445,7 +3577,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>399</v>
       </c>
@@ -3456,7 +3588,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>400</v>
       </c>
@@ -3464,10 +3596,10 @@
         <v>215</v>
       </c>
       <c r="C151">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>403</v>
       </c>
@@ -3478,7 +3610,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>404</v>
       </c>
@@ -3489,7 +3621,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>405</v>
       </c>
@@ -3497,10 +3629,10 @@
         <v>417</v>
       </c>
       <c r="C154">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>409</v>
       </c>
@@ -3511,7 +3643,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>415</v>
       </c>
@@ -3522,7 +3654,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>417</v>
       </c>
@@ -3533,7 +3665,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>421</v>
       </c>
@@ -3544,7 +3676,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>422</v>
       </c>
@@ -3555,7 +3687,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>423</v>
       </c>
@@ -3566,7 +3698,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>425</v>
       </c>
@@ -3574,10 +3706,10 @@
         <v>22</v>
       </c>
       <c r="C161">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>427</v>
       </c>
@@ -3588,7 +3720,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>429</v>
       </c>
@@ -3599,7 +3731,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>434</v>
       </c>
@@ -3610,7 +3742,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>435</v>
       </c>
@@ -3621,7 +3753,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>436</v>
       </c>
@@ -3632,7 +3764,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>440</v>
       </c>
@@ -3643,7 +3775,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>448</v>
       </c>
@@ -3651,10 +3783,10 @@
         <v>98</v>
       </c>
       <c r="C168">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
+        <v>4.0199999999999996</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>449</v>
       </c>
@@ -3662,10 +3794,10 @@
         <v>4046</v>
       </c>
       <c r="C169">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>450</v>
       </c>
@@ -3673,10 +3805,10 @@
         <v>140</v>
       </c>
       <c r="C170">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>453</v>
       </c>
@@ -3687,7 +3819,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>454</v>
       </c>
@@ -3695,10 +3827,10 @@
         <v>90</v>
       </c>
       <c r="C172">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>459</v>
       </c>
@@ -3709,7 +3841,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>460</v>
       </c>
@@ -3720,7 +3852,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>462</v>
       </c>
@@ -3731,7 +3863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>464</v>
       </c>
@@ -3742,7 +3874,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>469</v>
       </c>
@@ -3753,7 +3885,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>470</v>
       </c>
@@ -3764,7 +3896,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>474</v>
       </c>
@@ -3775,7 +3907,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>475</v>
       </c>
@@ -3783,10 +3915,10 @@
         <v>108</v>
       </c>
       <c r="C180">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>476</v>
       </c>
@@ -3797,7 +3929,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>479</v>
       </c>
@@ -3808,7 +3940,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>480</v>
       </c>
@@ -3819,7 +3951,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>482</v>
       </c>
@@ -3830,7 +3962,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>484</v>
       </c>
@@ -3838,10 +3970,10 @@
         <v>108</v>
       </c>
       <c r="C185">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>486</v>
       </c>
@@ -3849,10 +3981,10 @@
         <v>10</v>
       </c>
       <c r="C186">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>488</v>
       </c>
@@ -3863,7 +3995,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>489</v>
       </c>
@@ -3874,7 +4006,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>493</v>
       </c>
@@ -3885,7 +4017,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>494</v>
       </c>
@@ -3896,7 +4028,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>495</v>
       </c>
@@ -3907,7 +4039,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>497</v>
       </c>
@@ -3918,7 +4050,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>499</v>
       </c>
@@ -3929,7 +4061,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>500</v>
       </c>
@@ -3940,7 +4072,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>501</v>
       </c>
@@ -3951,7 +4083,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>505</v>
       </c>
@@ -3962,7 +4094,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>509</v>
       </c>
@@ -3973,7 +4105,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>513</v>
       </c>
@@ -3981,10 +4113,10 @@
         <v>80</v>
       </c>
       <c r="C198">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
+        <v>4.4400000000000004</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>517</v>
       </c>
@@ -3995,7 +4127,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>519</v>
       </c>
@@ -4006,7 +4138,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>520</v>
       </c>
@@ -4017,7 +4149,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>529</v>
       </c>
@@ -4025,10 +4157,10 @@
         <v>1496</v>
       </c>
       <c r="C202">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>544</v>
       </c>
@@ -4039,7 +4171,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>545</v>
       </c>
@@ -4047,10 +4179,10 @@
         <v>173</v>
       </c>
       <c r="C204">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>549</v>
       </c>
@@ -4061,7 +4193,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>555</v>
       </c>
@@ -4072,7 +4204,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>559</v>
       </c>
@@ -4083,7 +4215,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="208" spans="1:3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>565</v>
       </c>
@@ -4091,10 +4223,10 @@
         <v>51</v>
       </c>
       <c r="C208">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3">
+        <v>2.4900000000000002</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>569</v>
       </c>
@@ -4105,7 +4237,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>575</v>
       </c>
@@ -4116,7 +4248,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>577</v>
       </c>
@@ -4124,10 +4256,10 @@
         <v>661</v>
       </c>
       <c r="C211">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3">
+        <v>4.2300000000000004</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>581</v>
       </c>
@@ -4138,7 +4270,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>585</v>
       </c>
@@ -4149,7 +4281,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>590</v>
       </c>
@@ -4160,7 +4292,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>594</v>
       </c>
@@ -4171,7 +4303,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>599</v>
       </c>
@@ -4182,7 +4314,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>606</v>
       </c>
@@ -4193,7 +4325,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>615</v>
       </c>
@@ -4204,7 +4336,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>619</v>
       </c>
@@ -4215,7 +4347,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>625</v>
       </c>
@@ -4226,7 +4358,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>629</v>
       </c>
@@ -4237,7 +4369,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>631</v>
       </c>
@@ -4245,10 +4377,10 @@
         <v>35</v>
       </c>
       <c r="C222">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
+        <v>4.2300000000000004</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>645</v>
       </c>
@@ -4256,10 +4388,10 @@
         <v>110</v>
       </c>
       <c r="C223">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>648</v>
       </c>
@@ -4267,10 +4399,10 @@
         <v>1480</v>
       </c>
       <c r="C224">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>649</v>
       </c>
@@ -4278,10 +4410,10 @@
         <v>1911</v>
       </c>
       <c r="C225">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>652</v>
       </c>
@@ -4292,7 +4424,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="227" spans="1:3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>655</v>
       </c>
@@ -4303,7 +4435,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>659</v>
       </c>
@@ -4314,7 +4446,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="229" spans="1:3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>665</v>
       </c>
@@ -4325,7 +4457,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>669</v>
       </c>
@@ -4336,7 +4468,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>674</v>
       </c>
@@ -4347,7 +4479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>675</v>
       </c>
@@ -4358,7 +4490,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>678</v>
       </c>
@@ -4366,10 +4498,10 @@
         <v>10</v>
       </c>
       <c r="C233">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>684</v>
       </c>
@@ -4380,7 +4512,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>690</v>
       </c>
@@ -4391,7 +4523,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>699</v>
       </c>
@@ -4402,7 +4534,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="237" spans="1:3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>700</v>
       </c>
@@ -4413,7 +4545,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>701</v>
       </c>
@@ -4424,7 +4556,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>719</v>
       </c>
@@ -4435,7 +4567,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>725</v>
       </c>
@@ -4446,7 +4578,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>739</v>
       </c>
@@ -4457,7 +4589,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="242" spans="1:3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>741</v>
       </c>
@@ -4465,10 +4597,10 @@
         <v>10</v>
       </c>
       <c r="C242">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>742</v>
       </c>
@@ -4476,10 +4608,10 @@
         <v>100</v>
       </c>
       <c r="C243">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
+        <v>4.7300000000000004</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>749</v>
       </c>
@@ -4490,7 +4622,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>759</v>
       </c>
@@ -4501,7 +4633,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="246" spans="1:3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>766</v>
       </c>
@@ -4512,7 +4644,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>777</v>
       </c>
@@ -4523,7 +4655,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>785</v>
       </c>
@@ -4534,7 +4666,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>789</v>
       </c>
@@ -4545,7 +4677,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>792</v>
       </c>
@@ -4556,7 +4688,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="251" spans="1:3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>797</v>
       </c>
@@ -4567,7 +4699,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>799</v>
       </c>
@@ -4578,7 +4710,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>809</v>
       </c>
@@ -4589,7 +4721,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>828</v>
       </c>
@@ -4600,7 +4732,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>834</v>
       </c>
@@ -4611,7 +4743,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>849</v>
       </c>
@@ -4622,7 +4754,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>850</v>
       </c>
@@ -4630,10 +4762,10 @@
         <v>9</v>
       </c>
       <c r="C257">
-        <v>4.89</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3">
+        <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>852</v>
       </c>
@@ -4644,7 +4776,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>854</v>
       </c>
@@ -4655,7 +4787,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>859</v>
       </c>
@@ -4666,7 +4798,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>872</v>
       </c>
@@ -4677,7 +4809,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>889</v>
       </c>
@@ -4688,7 +4820,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>890</v>
       </c>
@@ -4696,10 +4828,10 @@
         <v>98</v>
       </c>
       <c r="C263">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>899</v>
       </c>
@@ -4710,7 +4842,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="265" spans="1:3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>901</v>
       </c>
@@ -4721,7 +4853,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="266" spans="1:3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>912</v>
       </c>
@@ -4732,7 +4864,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>944</v>
       </c>
@@ -4743,7 +4875,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>945</v>
       </c>
@@ -4754,7 +4886,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>949</v>
       </c>
@@ -4765,7 +4897,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="270" spans="1:3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>952</v>
       </c>
@@ -4776,7 +4908,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>980</v>
       </c>
@@ -4787,7 +4919,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="272" spans="1:3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>988</v>
       </c>
@@ -4798,7 +4930,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>989</v>
       </c>
@@ -4809,7 +4941,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="274" spans="1:3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>997</v>
       </c>
@@ -4820,7 +4952,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>999</v>
       </c>
@@ -4831,7 +4963,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>1095</v>
       </c>
@@ -4839,10 +4971,10 @@
         <v>861</v>
       </c>
       <c r="C276">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>1097</v>
       </c>
@@ -4853,7 +4985,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>1099</v>
       </c>
@@ -4864,7 +4996,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>1110</v>
       </c>
@@ -4872,10 +5004,10 @@
         <v>98</v>
       </c>
       <c r="C279">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>1119</v>
       </c>
@@ -4886,7 +5018,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>1142</v>
       </c>
@@ -4897,7 +5029,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>1149</v>
       </c>
@@ -4908,7 +5040,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>1155</v>
       </c>
@@ -4916,10 +5048,10 @@
         <v>37</v>
       </c>
       <c r="C283">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>1169</v>
       </c>
@@ -4930,7 +5062,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>1199</v>
       </c>
@@ -4941,7 +5073,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>1220</v>
       </c>
@@ -4952,7 +5084,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>1233</v>
       </c>
@@ -4963,7 +5095,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>1249</v>
       </c>
@@ -4974,7 +5106,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>1256</v>
       </c>
@@ -4985,7 +5117,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>1259</v>
       </c>
@@ -4993,10 +5125,10 @@
         <v>10</v>
       </c>
       <c r="C290">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>1260</v>
       </c>
@@ -5007,7 +5139,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>1278</v>
       </c>
@@ -5015,10 +5147,10 @@
         <v>91</v>
       </c>
       <c r="C292">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>1290</v>
       </c>
@@ -5029,7 +5161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>1298</v>
       </c>
@@ -5040,7 +5172,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="295" spans="1:3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>1299</v>
       </c>
@@ -5051,7 +5183,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>1329</v>
       </c>
@@ -5062,7 +5194,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>1349</v>
       </c>
@@ -5073,7 +5205,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>1383</v>
       </c>
@@ -5084,7 +5216,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>1399</v>
       </c>
@@ -5095,7 +5227,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="300" spans="1:3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>1401</v>
       </c>
@@ -5103,10 +5235,10 @@
         <v>81</v>
       </c>
       <c r="C300">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>1448</v>
       </c>
@@ -5117,7 +5249,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>1449</v>
       </c>
@@ -5128,7 +5260,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>1453</v>
       </c>
@@ -5139,7 +5271,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>1469</v>
       </c>
@@ -5150,7 +5282,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>1471</v>
       </c>
@@ -5161,7 +5293,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>1499</v>
       </c>
@@ -5172,7 +5304,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>1529</v>
       </c>
@@ -5183,7 +5315,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>1547</v>
       </c>
@@ -5191,10 +5323,10 @@
         <v>137</v>
       </c>
       <c r="C308">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>1549</v>
       </c>
@@ -5205,7 +5337,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="310" spans="1:3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>1550</v>
       </c>
@@ -5216,7 +5348,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>1565</v>
       </c>
@@ -5227,7 +5359,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="312" spans="1:3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>1599</v>
       </c>
@@ -5235,10 +5367,10 @@
         <v>3578</v>
       </c>
       <c r="C312">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>1614</v>
       </c>
@@ -5249,7 +5381,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>1649</v>
       </c>
@@ -5260,7 +5392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>1699</v>
       </c>
@@ -5271,7 +5403,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="316" spans="1:3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>1709</v>
       </c>
@@ -5282,7 +5414,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="317" spans="1:3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>1719</v>
       </c>
@@ -5293,7 +5425,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="318" spans="1:3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>1727</v>
       </c>
@@ -5301,10 +5433,10 @@
         <v>19</v>
       </c>
       <c r="C318">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>1747</v>
       </c>
@@ -5315,7 +5447,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>1782</v>
       </c>
@@ -5326,7 +5458,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>1799</v>
       </c>
@@ -5337,7 +5469,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>1804</v>
       </c>
@@ -5348,7 +5480,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>1819</v>
       </c>
@@ -5359,7 +5491,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>1839</v>
       </c>
@@ -5370,7 +5502,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>1899</v>
       </c>
@@ -5381,7 +5513,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>1999</v>
       </c>
@@ -5392,7 +5524,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>2069</v>
       </c>
@@ -5403,7 +5535,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="328" spans="1:3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>2096</v>
       </c>
@@ -5414,7 +5546,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>2099</v>
       </c>
@@ -5425,7 +5557,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>2119</v>
       </c>
@@ -5436,7 +5568,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>2125</v>
       </c>
@@ -5447,7 +5579,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>2152</v>
       </c>
@@ -5455,10 +5587,10 @@
         <v>199</v>
       </c>
       <c r="C332">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>2190</v>
       </c>
@@ -5469,7 +5601,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>2199</v>
       </c>
@@ -5480,7 +5612,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>2299</v>
       </c>
@@ -5491,7 +5623,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="336" spans="1:3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>2345</v>
       </c>
@@ -5499,10 +5631,10 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>2390</v>
       </c>
@@ -5513,7 +5645,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>2399</v>
       </c>
@@ -5524,7 +5656,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>2454</v>
       </c>
@@ -5535,7 +5667,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>2490</v>
       </c>
@@ -5546,7 +5678,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>2499</v>
       </c>
@@ -5557,7 +5689,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>2590</v>
       </c>
@@ -5565,10 +5697,10 @@
         <v>187</v>
       </c>
       <c r="C342">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>2599</v>
       </c>
@@ -5579,7 +5711,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>2651</v>
       </c>
@@ -5590,7 +5722,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>2690</v>
       </c>
@@ -5601,7 +5733,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>2692</v>
       </c>
@@ -5609,10 +5741,10 @@
         <v>29</v>
       </c>
       <c r="C346">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>2695</v>
       </c>
@@ -5620,10 +5752,10 @@
         <v>121</v>
       </c>
       <c r="C347">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>2699</v>
       </c>
@@ -5631,10 +5763,10 @@
         <v>132</v>
       </c>
       <c r="C348">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>2709</v>
       </c>
@@ -5645,7 +5777,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>2799</v>
       </c>
@@ -5656,7 +5788,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>2819</v>
       </c>
@@ -5667,7 +5799,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>2879</v>
       </c>
@@ -5675,10 +5807,10 @@
         <v>175</v>
       </c>
       <c r="C352">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3">
+        <v>4.0199999999999996</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>2949</v>
       </c>
@@ -5686,10 +5818,10 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>2969</v>
       </c>
@@ -5700,7 +5832,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>2970</v>
       </c>
@@ -5711,7 +5843,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="356" spans="1:3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>2990</v>
       </c>
@@ -5722,7 +5854,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>2995</v>
       </c>
@@ -5733,7 +5865,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="358" spans="1:3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>2999</v>
       </c>
@@ -5744,7 +5876,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="359" spans="1:3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>3035</v>
       </c>
@@ -5755,7 +5887,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="360" spans="1:3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>3039</v>
       </c>
@@ -5766,7 +5898,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="361" spans="1:3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>3059</v>
       </c>
@@ -5777,7 +5909,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="362" spans="1:3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>3149</v>
       </c>
@@ -5788,7 +5920,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="363" spans="1:3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>3199</v>
       </c>
@@ -5799,7 +5931,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="364" spans="1:3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>3249</v>
       </c>
@@ -5810,7 +5942,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="365" spans="1:3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>3268</v>
       </c>
@@ -5821,7 +5953,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="366" spans="1:3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>3295</v>
       </c>
@@ -5832,7 +5964,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>3307</v>
       </c>
@@ -5843,7 +5975,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="368" spans="1:3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>3399</v>
       </c>
@@ -5854,7 +5986,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>3479</v>
       </c>
@@ -5865,7 +5997,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="370" spans="1:3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>3499</v>
       </c>
@@ -5876,7 +6008,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>3569</v>
       </c>
@@ -5887,7 +6019,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="372" spans="1:3">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>3595</v>
       </c>
@@ -5895,10 +6027,10 @@
         <v>66</v>
       </c>
       <c r="C372">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>3599</v>
       </c>
@@ -5909,7 +6041,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="374" spans="1:3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>3661</v>
       </c>
@@ -5920,7 +6052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:3">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>3699</v>
       </c>
@@ -5928,10 +6060,10 @@
         <v>135</v>
       </c>
       <c r="C375">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3">
+        <v>4.4400000000000004</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>3746</v>
       </c>
@@ -5942,7 +6074,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="377" spans="1:3">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>3749</v>
       </c>
@@ -5953,7 +6085,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>3899</v>
       </c>
@@ -5964,7 +6096,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="379" spans="1:3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>3959</v>
       </c>
@@ -5975,7 +6107,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="380" spans="1:3">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>3999</v>
       </c>
@@ -5986,7 +6118,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="381" spans="1:3">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>4000</v>
       </c>
@@ -5997,7 +6129,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="382" spans="1:3">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>4079</v>
       </c>
@@ -6008,7 +6140,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="383" spans="1:3">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>4084</v>
       </c>
@@ -6019,7 +6151,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="384" spans="1:3">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>4098</v>
       </c>
@@ -6030,7 +6162,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="385" spans="1:3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>4199</v>
       </c>
@@ -6041,7 +6173,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="386" spans="1:3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>4219</v>
       </c>
@@ -6052,7 +6184,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="387" spans="1:3">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>4293</v>
       </c>
@@ -6060,10 +6192,10 @@
         <v>42</v>
       </c>
       <c r="C387">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>4319</v>
       </c>
@@ -6071,10 +6203,10 @@
         <v>118</v>
       </c>
       <c r="C388">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>4330</v>
       </c>
@@ -6085,7 +6217,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="390" spans="1:3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>4366</v>
       </c>
@@ -6096,7 +6228,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="391" spans="1:3">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>4396</v>
       </c>
@@ -6107,7 +6239,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="392" spans="1:3">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>4399</v>
       </c>
@@ -6118,7 +6250,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>4449</v>
       </c>
@@ -6129,7 +6261,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="394" spans="1:3">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>4498</v>
       </c>
@@ -6140,7 +6272,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="395" spans="1:3">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>4499</v>
       </c>
@@ -6151,7 +6283,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="396" spans="1:3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>4687</v>
       </c>
@@ -6162,7 +6294,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="397" spans="1:3">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>4699</v>
       </c>
@@ -6170,10 +6302,10 @@
         <v>135</v>
       </c>
       <c r="C397">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>4715</v>
       </c>
@@ -6181,10 +6313,10 @@
         <v>96</v>
       </c>
       <c r="C398">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>4899</v>
       </c>
@@ -6195,7 +6327,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="400" spans="1:3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>4979</v>
       </c>
@@ -6206,7 +6338,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>4999</v>
       </c>
@@ -6217,7 +6349,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>5039</v>
       </c>
@@ -6228,7 +6360,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>5079</v>
       </c>
@@ -6236,10 +6368,10 @@
         <v>371</v>
       </c>
       <c r="C403">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3">
+        <v>4.0199999999999996</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>5149</v>
       </c>
@@ -6250,7 +6382,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>5190</v>
       </c>
@@ -6258,10 +6390,10 @@
         <v>195</v>
       </c>
       <c r="C405">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>5298</v>
       </c>
@@ -6272,7 +6404,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>5299</v>
       </c>
@@ -6283,7 +6415,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>5300</v>
       </c>
@@ -6294,7 +6426,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="409" spans="1:3">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>5390</v>
       </c>
@@ -6305,7 +6437,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>5414</v>
       </c>
@@ -6316,7 +6448,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="411" spans="1:3">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>5499</v>
       </c>
@@ -6327,7 +6459,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="412" spans="1:3">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>5599</v>
       </c>
@@ -6338,7 +6470,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>5790</v>
       </c>
@@ -6349,7 +6481,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="414" spans="1:3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>5890</v>
       </c>
@@ -6357,10 +6489,10 @@
         <v>100</v>
       </c>
       <c r="C414">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3">
+        <v>4.0199999999999996</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>5919</v>
       </c>
@@ -6371,7 +6503,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="416" spans="1:3">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>5959</v>
       </c>
@@ -6382,7 +6514,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="417" spans="1:3">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417">
         <v>5990</v>
       </c>
@@ -6390,10 +6522,10 @@
         <v>278</v>
       </c>
       <c r="C417">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418">
         <v>5993</v>
       </c>
@@ -6401,10 +6533,10 @@
         <v>98</v>
       </c>
       <c r="C418">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419">
         <v>5999</v>
       </c>
@@ -6412,10 +6544,10 @@
         <v>119</v>
       </c>
       <c r="C419">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420">
         <v>6029</v>
       </c>
@@ -6426,7 +6558,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="421" spans="1:3">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421">
         <v>6099</v>
       </c>
@@ -6437,7 +6569,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="422" spans="1:3">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422">
         <v>6195</v>
       </c>
@@ -6448,7 +6580,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="423" spans="1:3">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423">
         <v>6299</v>
       </c>
@@ -6459,7 +6591,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="424" spans="1:3">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424">
         <v>6387</v>
       </c>
@@ -6467,10 +6599,10 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425">
         <v>6390</v>
       </c>
@@ -6481,7 +6613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:3">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426">
         <v>6495</v>
       </c>
@@ -6492,7 +6624,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="427" spans="1:3">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427">
         <v>6498</v>
       </c>
@@ -6503,7 +6635,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="428" spans="1:3">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428">
         <v>6499</v>
       </c>
@@ -6514,7 +6646,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="429" spans="1:3">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429">
         <v>6505</v>
       </c>
@@ -6525,7 +6657,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="430" spans="1:3">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430">
         <v>6525</v>
       </c>
@@ -6536,7 +6668,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="431" spans="1:3">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431">
         <v>6589</v>
       </c>
@@ -6547,7 +6679,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="432" spans="1:3">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432">
         <v>6591</v>
       </c>
@@ -6558,7 +6690,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="433" spans="1:3">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433">
         <v>6690</v>
       </c>
@@ -6569,7 +6701,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="434" spans="1:3">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434">
         <v>6719</v>
       </c>
@@ -6580,7 +6712,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="435" spans="1:3">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435">
         <v>6949</v>
       </c>
@@ -6591,7 +6723,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="436" spans="1:3">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436">
         <v>6999</v>
       </c>
@@ -6599,10 +6731,10 @@
         <v>1316</v>
       </c>
       <c r="C436">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437">
         <v>7079</v>
       </c>
@@ -6613,7 +6745,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="438" spans="1:3">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438">
         <v>7299</v>
       </c>
@@ -6621,10 +6753,10 @@
         <v>398</v>
       </c>
       <c r="C438">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439">
         <v>7493</v>
       </c>
@@ -6635,7 +6767,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="440" spans="1:3">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440">
         <v>7499</v>
       </c>
@@ -6646,7 +6778,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="441" spans="1:3">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441">
         <v>7599</v>
       </c>
@@ -6654,10 +6786,10 @@
         <v>435</v>
       </c>
       <c r="C441">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442">
         <v>7609</v>
       </c>
@@ -6665,10 +6797,10 @@
         <v>100</v>
       </c>
       <c r="C442">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3">
+        <v>4.4400000000000004</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443">
         <v>7649</v>
       </c>
@@ -6679,7 +6811,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="444" spans="1:3">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444">
         <v>7690</v>
       </c>
@@ -6690,7 +6822,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="445" spans="1:3">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445">
         <v>7759</v>
       </c>
@@ -6701,7 +6833,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="446" spans="1:3">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446">
         <v>7799</v>
       </c>
@@ -6712,7 +6844,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="447" spans="1:3">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447">
         <v>7909</v>
       </c>
@@ -6723,7 +6855,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="448" spans="1:3">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448">
         <v>7999</v>
       </c>
@@ -6734,7 +6866,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449">
         <v>8199</v>
       </c>
@@ -6742,10 +6874,10 @@
         <v>389</v>
       </c>
       <c r="C449">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450">
         <v>8449</v>
       </c>
@@ -6756,7 +6888,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451">
         <v>8490</v>
       </c>
@@ -6767,7 +6899,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452">
         <v>8499</v>
       </c>
@@ -6778,7 +6910,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453">
         <v>8590</v>
       </c>
@@ -6789,7 +6921,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="454" spans="1:3">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454">
         <v>8699</v>
       </c>
@@ -6797,10 +6929,10 @@
         <v>30</v>
       </c>
       <c r="C454">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455">
         <v>8790</v>
       </c>
@@ -6811,7 +6943,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="456" spans="1:3">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456">
         <v>8797</v>
       </c>
@@ -6822,7 +6954,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="457" spans="1:3">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457">
         <v>8799</v>
       </c>
@@ -6833,7 +6965,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="458" spans="1:3">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458">
         <v>8890</v>
       </c>
@@ -6844,7 +6976,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="459" spans="1:3">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459">
         <v>8999</v>
       </c>
@@ -6855,7 +6987,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="460" spans="1:3">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460">
         <v>9050</v>
       </c>
@@ -6863,10 +6995,10 @@
         <v>100</v>
       </c>
       <c r="C460">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3">
+        <v>4.0599999999999996</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461">
         <v>9190</v>
       </c>
@@ -6877,7 +7009,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="462" spans="1:3">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462">
         <v>9499</v>
       </c>
@@ -6888,7 +7020,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="463" spans="1:3">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463">
         <v>9799</v>
       </c>
@@ -6899,7 +7031,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="464" spans="1:3">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464">
         <v>9950</v>
       </c>
@@ -6907,10 +7039,10 @@
         <v>10</v>
       </c>
       <c r="C464">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465">
         <v>9990</v>
       </c>
@@ -6921,7 +7053,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="466" spans="1:3">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466">
         <v>9999</v>
       </c>
@@ -6929,10 +7061,10 @@
         <v>1430</v>
       </c>
       <c r="C466">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3">
+        <v>4.1100000000000003</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467">
         <v>10000</v>
       </c>
@@ -6940,10 +7072,10 @@
         <v>23</v>
       </c>
       <c r="C467">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468">
         <v>10790</v>
       </c>
@@ -6954,7 +7086,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="469" spans="1:3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469">
         <v>10890</v>
       </c>
@@ -6965,7 +7097,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="470" spans="1:3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470">
         <v>11440</v>
       </c>
@@ -6976,7 +7108,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="471" spans="1:3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471">
         <v>11500</v>
       </c>
@@ -6987,7 +7119,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="472" spans="1:3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472">
         <v>11595</v>
       </c>
@@ -6995,10 +7127,10 @@
         <v>25</v>
       </c>
       <c r="C472">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473">
         <v>11690</v>
       </c>
@@ -7009,7 +7141,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474">
         <v>11999</v>
       </c>
@@ -7017,10 +7149,10 @@
         <v>112</v>
       </c>
       <c r="C474">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475">
         <v>12881</v>
       </c>
@@ -7031,7 +7163,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="476" spans="1:3">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476">
         <v>12990</v>
       </c>
@@ -7042,7 +7174,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="477" spans="1:3">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477">
         <v>12999</v>
       </c>
@@ -7053,7 +7185,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="478" spans="1:3">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478">
         <v>13049</v>
       </c>
@@ -7064,7 +7196,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="479" spans="1:3">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479">
         <v>13703</v>
       </c>
@@ -7075,7 +7207,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="480" spans="1:3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480">
         <v>13999</v>
       </c>
@@ -7083,10 +7215,10 @@
         <v>3029</v>
       </c>
       <c r="C480">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481">
         <v>14146</v>
       </c>
@@ -7097,7 +7229,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="482" spans="1:3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482">
         <v>14190</v>
       </c>
@@ -7108,7 +7240,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="483" spans="1:3">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A483">
         <v>14299</v>
       </c>
@@ -7119,7 +7251,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="484" spans="1:3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A484">
         <v>14790</v>
       </c>
@@ -7130,7 +7262,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="485" spans="1:3">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A485">
         <v>14999</v>
       </c>
@@ -7141,7 +7273,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="486" spans="1:3">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A486">
         <v>15490</v>
       </c>
@@ -7152,7 +7284,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A487">
         <v>15999</v>
       </c>
@@ -7160,10 +7292,10 @@
         <v>440</v>
       </c>
       <c r="C487">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3">
+        <v>4.0199999999999996</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A488">
         <v>16490</v>
       </c>
@@ -7171,10 +7303,10 @@
         <v>266</v>
       </c>
       <c r="C488">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A489">
         <v>16499</v>
       </c>
@@ -7185,7 +7317,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="490" spans="1:3">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A490">
         <v>16990</v>
       </c>
@@ -7193,10 +7325,10 @@
         <v>555</v>
       </c>
       <c r="C490">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3">
+        <v>4.1900000000000004</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A491">
         <v>18990</v>
       </c>
@@ -7207,7 +7339,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="492" spans="1:3">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A492">
         <v>20990</v>
       </c>
@@ -7218,7 +7350,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="493" spans="1:3">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A493">
         <v>23479</v>
       </c>
@@ -7226,10 +7358,10 @@
         <v>27</v>
       </c>
       <c r="C493">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A494">
         <v>24490</v>
       </c>
@@ -7240,7 +7372,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="495" spans="1:3">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A495">
         <v>25499</v>
       </c>
@@ -7251,7 +7383,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="496" spans="1:3">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A496">
         <v>25990</v>
       </c>
@@ -7262,7 +7394,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="497" spans="1:3">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A497">
         <v>26990</v>
       </c>
@@ -7273,7 +7405,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="498" spans="1:3">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A498">
         <v>27490</v>
       </c>
@@ -7281,10 +7413,10 @@
         <v>31</v>
       </c>
       <c r="C498">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A499">
         <v>27999</v>
       </c>
@@ -7292,10 +7424,10 @@
         <v>629</v>
       </c>
       <c r="C499">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A500">
         <v>29390</v>
       </c>
@@ -7306,7 +7438,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="501" spans="1:3">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A501">
         <v>29990</v>
       </c>
@@ -7314,10 +7446,10 @@
         <v>1324</v>
       </c>
       <c r="C501">
-        <v>4.65</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A502">
         <v>30999</v>
       </c>
@@ -7328,7 +7460,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="503" spans="1:3">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A503">
         <v>31590</v>
       </c>
@@ -7339,7 +7471,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="504" spans="1:3">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A504">
         <v>33990</v>
       </c>
@@ -7350,7 +7482,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="505" spans="1:3">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A505">
         <v>38490</v>
       </c>
@@ -7358,10 +7490,10 @@
         <v>170</v>
       </c>
       <c r="C505">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3">
+        <v>4.3899999999999997</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A506">
         <v>38990</v>
       </c>
@@ -7372,7 +7504,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="507" spans="1:3">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A507">
         <v>41990</v>
       </c>
@@ -7380,10 +7512,10 @@
         <v>142</v>
       </c>
       <c r="C507">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A508">
         <v>42000</v>
       </c>
@@ -7394,7 +7526,7 @@
         <v>4.38</v>
       </c>
     </row>
-    <row r="509" spans="1:3">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A509">
         <v>44490</v>
       </c>
@@ -7402,10 +7534,10 @@
         <v>150</v>
       </c>
       <c r="C509">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A510">
         <v>44890</v>
       </c>
@@ -7416,7 +7548,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="511" spans="1:3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A511">
         <v>45550</v>
       </c>
@@ -7427,7 +7559,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="512" spans="1:3">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A512">
         <v>46990</v>
       </c>
@@ -7435,10 +7567,10 @@
         <v>72</v>
       </c>
       <c r="C512">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A513">
         <v>46999</v>
       </c>
@@ -7449,7 +7581,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="514" spans="1:3">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A514">
         <v>50999</v>
       </c>
@@ -7457,10 +7589,10 @@
         <v>13</v>
       </c>
       <c r="C514">
-        <v>4.31</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A515">
         <v>51990</v>
       </c>
@@ -7468,10 +7600,10 @@
         <v>36</v>
       </c>
       <c r="C515">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3">
+        <v>4.3899999999999997</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A516">
         <v>52990</v>
       </c>
@@ -7482,7 +7614,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="517" spans="1:3">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A517">
         <v>58990</v>
       </c>
@@ -7493,7 +7625,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="518" spans="1:3">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A518">
         <v>59990</v>
       </c>
@@ -7504,7 +7636,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="519" spans="1:3">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A519">
         <v>63600</v>
       </c>
@@ -7515,7 +7647,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="520" spans="1:3">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A520">
         <v>63990</v>
       </c>
@@ -7526,7 +7658,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="521" spans="1:3">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A521">
         <v>66990</v>
       </c>
@@ -7534,10 +7666,10 @@
         <v>70</v>
       </c>
       <c r="C521">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A522">
         <v>67490</v>
       </c>
@@ -7548,7 +7680,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="523" spans="1:3">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A523">
         <v>86990</v>
       </c>
@@ -7565,16 +7697,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="4" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.7265625" customWidth="1"/>
+    <col min="2" max="4" width="22.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="28" customHeight="1">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
@@ -7585,7 +7717,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -7596,7 +7728,7 @@
         <v>11.47</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -7607,7 +7739,7 @@
         <v>13.72</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>65</v>
       </c>
